--- a/GT_JUNE_26/30-06-26/Mubeen.xlsx
+++ b/GT_JUNE_26/30-06-26/Mubeen.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{971F473A-848F-433D-A57E-13F96AF8D1C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BADC1E3-1EA0-4516-8F72-5CE2DA886C72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="13" r:id="rId1"/>
@@ -3417,7 +3417,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -3445,7 +3445,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -4654,7 +4654,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -4682,7 +4682,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -5887,7 +5887,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -5915,7 +5915,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -7108,7 +7108,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -7136,7 +7136,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -8329,7 +8329,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -8357,7 +8357,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -9550,7 +9550,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -9578,7 +9578,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -10768,7 +10768,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -10796,7 +10796,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -11985,7 +11985,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -12013,7 +12013,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -13202,7 +13202,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -13230,7 +13230,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -14419,7 +14419,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -14447,7 +14447,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -18386,7 +18386,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -18414,7 +18414,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -19603,7 +19603,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -19631,7 +19631,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -20820,7 +20820,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -20848,7 +20848,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -22037,7 +22037,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -22065,7 +22065,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -23259,7 +23259,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -23287,7 +23287,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -23498,7 +23498,7 @@
       </c>
       <c r="U14" s="164">
         <f>+'1'!P35</f>
-        <v>2560.6933883000002</v>
+        <v>0</v>
       </c>
       <c r="XFD14" t="s">
         <v>75</v>
@@ -23584,11 +23584,11 @@
       <c r="G16" s="114"/>
       <c r="H16" s="172">
         <f>+'1'!H16+'2'!H16+'4'!H16+'3'!H16+'5'!H16+'6'!H16+'7'!H16+'8'!H16+'9'!H16+'10'!H16+'11'!H16+'12'!H16+'13'!H16+'14'!H16+'15'!H16+'16'!H16</f>
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="I16" s="1">
         <f>(G16*D16)*F16+H16*F16</f>
-        <v>1364.0249999999999</v>
+        <v>1049.25</v>
       </c>
       <c r="J16" s="172">
         <f>+'1'!J16+'2'!J16+'4'!J16+'3'!J16+'5'!J16+'6'!J16+'7'!J16+'8'!J16+'9'!J16+'10'!J16+'11'!J16+'12'!J16+'13'!J16+'14'!J16+'15'!J16+'16'!J16+'17'!J16+'18'!J16</f>
@@ -23600,23 +23600,23 @@
       </c>
       <c r="L16" s="175">
         <f>+'1'!L16+'2'!L16+'4'!L16+'3'!L16+'5'!L16+'6'!L16+'7'!L16+'8'!L16+'9'!L16+'10'!L16</f>
-        <v>109.122</v>
+        <v>83.94</v>
       </c>
       <c r="M16" s="106">
         <f>I16-K16-L16</f>
-        <v>1254.9029999999998</v>
+        <v>965.31</v>
       </c>
       <c r="N16" s="101">
         <f>+'1'!N16+'2'!N16+'4'!N16+'3'!N16+'5'!N16+'6'!N16+'7'!N16+'8'!N16+'9'!N16+'10'!N16</f>
-        <v>287.62040999999999</v>
+        <v>223.90995000000001</v>
       </c>
       <c r="O16" s="101">
         <f>+'1'!O16+'2'!O16+'4'!O16+'3'!O16+'5'!O16+'6'!O16+'7'!O16+'8'!O16+'9'!O16+'10'!O16</f>
-        <v>7.7126170500000004</v>
+        <v>5.9460997500000001</v>
       </c>
       <c r="P16" s="105">
         <f t="shared" ref="P16:P24" si="0">M16+N16+O16</f>
-        <v>1550.2360270499998</v>
+        <v>1195.16604975</v>
       </c>
       <c r="Q16" s="108"/>
       <c r="T16" s="163" t="str">
@@ -23625,7 +23625,7 @@
       </c>
       <c r="U16" s="164">
         <f>+'3'!P35</f>
-        <v>2449.1066723100007</v>
+        <v>0</v>
       </c>
       <c r="XFD16" t="s">
         <v>82</v>
@@ -23658,11 +23658,11 @@
       <c r="G17" s="114"/>
       <c r="H17" s="172">
         <f>+'1'!H17+'2'!H17+'4'!H17+'3'!H17+'5'!H17+'6'!H17+'7'!H17+'8'!H17+'9'!H17+'10'!H17+'11'!H17+'12'!H17+'13'!H17+'14'!H17+'15'!H17+'16'!H17</f>
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="I17" s="1">
         <f t="shared" ref="I17:I23" si="1">(G17*D17)*F17+H17*F17</f>
-        <v>1364.0249999999999</v>
+        <v>1049.25</v>
       </c>
       <c r="J17" s="172">
         <f>+'1'!J17+'2'!J17+'4'!J17+'3'!J17+'5'!J17+'6'!J17+'7'!J17+'8'!J17+'9'!J17+'10'!J17+'11'!J17+'12'!J17+'13'!J17+'14'!J17+'15'!J17+'16'!J17+'17'!J17+'18'!J17</f>
@@ -23674,23 +23674,23 @@
       </c>
       <c r="L17" s="175">
         <f>+'1'!L17+'2'!L17+'4'!L17+'3'!L17+'5'!L17+'6'!L17+'7'!L17+'8'!L17+'9'!L17+'10'!L17</f>
-        <v>109.122</v>
+        <v>83.94</v>
       </c>
       <c r="M17" s="118">
         <f t="shared" ref="M17:M23" si="2">I17-K17-L17</f>
-        <v>1254.9029999999998</v>
+        <v>965.31</v>
       </c>
       <c r="N17" s="101">
         <f>+'1'!N17+'2'!N17+'4'!N17+'3'!N17+'5'!N17+'6'!N17+'7'!N17+'8'!N17+'9'!N17+'10'!N17</f>
-        <v>287.62040999999999</v>
+        <v>223.90995000000001</v>
       </c>
       <c r="O17" s="101">
         <f>+'1'!O17+'2'!O17+'4'!O17+'3'!O17+'5'!O17+'6'!O17+'7'!O17+'8'!O17+'9'!O17+'10'!O17</f>
-        <v>7.7126170500000004</v>
+        <v>5.9460997500000001</v>
       </c>
       <c r="P17" s="120">
         <f t="shared" si="0"/>
-        <v>1550.2360270499998</v>
+        <v>1195.16604975</v>
       </c>
       <c r="S17" s="64"/>
       <c r="T17" s="163" t="str">
@@ -23699,7 +23699,7 @@
       </c>
       <c r="U17" s="164">
         <f>+'4'!P35</f>
-        <v>538.64712270000007</v>
+        <v>0</v>
       </c>
       <c r="XFD17" t="s">
         <v>83</v>
@@ -23802,11 +23802,11 @@
       <c r="G19" s="114"/>
       <c r="H19" s="172">
         <f>+'1'!H19+'2'!H19+'4'!H19+'3'!H19+'5'!H19+'6'!H19+'7'!H19+'8'!H19+'9'!H19+'10'!H19+'11'!H19+'12'!H19+'13'!H19+'14'!H19+'15'!H19+'16'!H19</f>
-        <v>169</v>
+        <v>155</v>
       </c>
       <c r="I19" s="1">
         <f t="shared" si="1"/>
-        <v>12276.16</v>
+        <v>11259.2</v>
       </c>
       <c r="J19" s="172">
         <f>+'1'!J19+'2'!J19+'4'!J19+'3'!J19+'5'!J19+'6'!J19+'7'!J19+'8'!J19+'9'!J19+'10'!J19+'11'!J19+'12'!J19+'13'!J19+'14'!J19+'15'!J19+'16'!J19+'17'!J19+'18'!J19</f>
@@ -23818,23 +23818,23 @@
       </c>
       <c r="L19" s="175">
         <f>+'1'!L19+'2'!L19+'4'!L19+'3'!L19+'5'!L19+'6'!L19+'7'!L19+'8'!L19+'9'!L19+'10'!L19</f>
-        <v>982.09280000000012</v>
+        <v>900.73599999999999</v>
       </c>
       <c r="M19" s="118">
         <f t="shared" si="2"/>
-        <v>11294.0672</v>
+        <v>10358.464</v>
       </c>
       <c r="N19" s="101">
         <f>+'1'!N19+'2'!N19+'4'!N19+'3'!N19+'5'!N19+'6'!N19+'7'!N19+'8'!N19+'9'!N19+'10'!N19</f>
-        <v>2596.5603839999999</v>
+        <v>2390.72768</v>
       </c>
       <c r="O19" s="101">
         <f>+'1'!O19+'2'!O19+'4'!O19+'3'!O19+'5'!O19+'6'!O19+'7'!O19+'8'!O19+'9'!O19+'10'!O19</f>
-        <v>82.498119680000002</v>
+        <v>63.745958400000006</v>
       </c>
       <c r="P19" s="120">
         <f t="shared" si="0"/>
-        <v>13973.12570368</v>
+        <v>12812.937638400001</v>
       </c>
       <c r="T19" s="163" t="str">
         <f>+'6'!A5</f>
@@ -23842,7 +23842,7 @@
       </c>
       <c r="U19" s="164">
         <f>+'6'!P35</f>
-        <v>269.32356135000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:21 16384:16384" ht="29.25" customHeight="1" x14ac:dyDescent="0.6">
@@ -23872,15 +23872,15 @@
       <c r="G20" s="114"/>
       <c r="H20" s="172">
         <f>+'1'!H20+'2'!H20+'4'!H20+'3'!H20+'5'!H20+'6'!H20+'7'!H20+'8'!H20+'9'!H20+'10'!H20+'11'!H20+'12'!H20+'13'!H20+'14'!H20+'15'!H20+'16'!H20</f>
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="I20" s="1">
         <f t="shared" si="1"/>
-        <v>4648.96</v>
+        <v>3632</v>
       </c>
       <c r="J20" s="172">
         <f>+'1'!J20+'2'!J20+'4'!J20+'3'!J20+'5'!J20+'6'!J20+'7'!J20+'8'!J20+'9'!J20+'10'!J20+'11'!J20+'12'!J20+'13'!J20+'14'!J20+'15'!J20+'16'!J20+'17'!J20+'18'!J20</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K20" s="172">
         <f>+'1'!K20+'2'!K20+'4'!K20+'3'!K20+'5'!K20+'6'!K20+'7'!K20+'8'!K20+'9'!K20+'10'!K20</f>
@@ -23888,23 +23888,23 @@
       </c>
       <c r="L20" s="175">
         <f>+'1'!L20+'2'!L20+'4'!L20+'3'!L20+'5'!L20+'6'!L20+'7'!L20+'8'!L20+'9'!L20+'10'!L20</f>
-        <v>371.91680000000002</v>
+        <v>290.56</v>
       </c>
       <c r="M20" s="118">
         <f t="shared" si="2"/>
-        <v>4277.0432000000001</v>
+        <v>3341.44</v>
       </c>
       <c r="N20" s="101">
         <f>+'1'!N20+'2'!N20+'4'!N20+'3'!N20+'5'!N20+'6'!N20+'7'!N20+'8'!N20+'9'!N20+'10'!N20</f>
-        <v>1004.872704</v>
+        <v>783.05919999999992</v>
       </c>
       <c r="O20" s="101">
         <f>+'1'!O20+'2'!O20+'4'!O20+'3'!O20+'5'!O20+'6'!O20+'7'!O20+'8'!O20+'9'!O20+'10'!O20</f>
-        <v>39.774177280000004</v>
+        <v>20.622495999999998</v>
       </c>
       <c r="P20" s="120">
         <f t="shared" si="0"/>
-        <v>5321.6900812800004</v>
+        <v>4145.1216960000002</v>
       </c>
       <c r="T20" s="163" t="str">
         <f>+'7'!A5</f>
@@ -23942,11 +23942,11 @@
       <c r="G21" s="114"/>
       <c r="H21" s="172">
         <f>+'1'!H21+'2'!H21+'4'!H21+'3'!H21+'5'!H21+'6'!H21+'7'!H21+'8'!H21+'9'!H21+'10'!H21+'11'!H21+'12'!H21+'13'!H21+'14'!H21+'15'!H21+'16'!H21</f>
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="I21" s="1">
         <f t="shared" si="1"/>
-        <v>9370.56</v>
+        <v>8353.6</v>
       </c>
       <c r="J21" s="172">
         <f>+'1'!J21+'2'!J21+'4'!J21+'3'!J21+'5'!J21+'6'!J21+'7'!J21+'8'!J21+'9'!J21+'10'!J21+'11'!J21+'12'!J21+'13'!J21+'14'!J21+'15'!J21+'16'!J21+'17'!J21+'18'!J21</f>
@@ -23958,23 +23958,23 @@
       </c>
       <c r="L21" s="175">
         <f>+'1'!L21+'2'!L21+'4'!L21+'3'!L21+'5'!L21+'6'!L21+'7'!L21+'8'!L21+'9'!L21+'10'!L21</f>
-        <v>749.64480000000003</v>
+        <v>668.28800000000001</v>
       </c>
       <c r="M21" s="118">
         <f t="shared" si="2"/>
-        <v>8620.9151999999995</v>
+        <v>7685.3119999999999</v>
       </c>
       <c r="N21" s="101">
         <f>+'1'!N21+'2'!N21+'4'!N21+'3'!N21+'5'!N21+'6'!N21+'7'!N21+'8'!N21+'9'!N21+'10'!N21</f>
-        <v>1992.486144</v>
+        <v>1786.6534399999998</v>
       </c>
       <c r="O21" s="101">
         <f>+'1'!O21+'2'!O21+'4'!O21+'3'!O21+'5'!O21+'6'!O21+'7'!O21+'8'!O21+'9'!O21+'10'!O21</f>
-        <v>66.111988480000008</v>
+        <v>47.359827199999998</v>
       </c>
       <c r="P21" s="120">
         <f t="shared" si="0"/>
-        <v>10679.513332479999</v>
+        <v>9519.3252671999999</v>
       </c>
       <c r="T21" s="163" t="str">
         <f>+'8'!A5</f>
@@ -24012,11 +24012,11 @@
       <c r="G22" s="114"/>
       <c r="H22" s="172">
         <f>+'1'!H22+'2'!H22+'4'!H22+'3'!H22+'5'!H22+'6'!H22+'7'!H22+'8'!H22+'9'!H22+'10'!H22+'11'!H22+'12'!H22+'13'!H22+'14'!H22+'15'!H22+'16'!H22</f>
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="I22" s="1">
         <f t="shared" si="1"/>
-        <v>1412.2800000000002</v>
+        <v>0</v>
       </c>
       <c r="J22" s="172">
         <f>+'1'!J22+'2'!J22+'4'!J22+'3'!J22+'5'!J22+'6'!J22+'7'!J22+'8'!J22+'9'!J22+'10'!J22+'11'!J22+'12'!J22+'13'!J22+'14'!J22+'15'!J22+'16'!J22+'17'!J22+'18'!J22</f>
@@ -24024,27 +24024,27 @@
       </c>
       <c r="K22" s="172">
         <f>+'1'!K22+'2'!K22+'4'!K22+'3'!K22+'5'!K22+'6'!K22+'7'!K22+'8'!K22+'9'!K22+'10'!K22</f>
-        <v>49.429800000000014</v>
+        <v>0</v>
       </c>
       <c r="L22" s="175">
         <f>+'1'!L22+'2'!L22+'4'!L22+'3'!L22+'5'!L22+'6'!L22+'7'!L22+'8'!L22+'9'!L22+'10'!L22</f>
-        <v>70.614000000000019</v>
+        <v>0</v>
       </c>
       <c r="M22" s="118">
         <f t="shared" si="2"/>
-        <v>1292.2362000000001</v>
+        <v>0</v>
       </c>
       <c r="N22" s="101">
         <f>+'1'!N22+'2'!N22+'4'!N22+'3'!N22+'5'!N22+'6'!N22+'7'!N22+'8'!N22+'9'!N22+'10'!N22</f>
-        <v>284.29196400000001</v>
+        <v>0</v>
       </c>
       <c r="O22" s="101">
         <f>+'1'!O22+'2'!O22+'4'!O22+'3'!O22+'5'!O22+'6'!O22+'7'!O22+'8'!O22+'9'!O22+'10'!O22</f>
-        <v>34.158110220000012</v>
+        <v>0</v>
       </c>
       <c r="P22" s="120">
         <f t="shared" si="0"/>
-        <v>1610.6862742200001</v>
+        <v>0</v>
       </c>
       <c r="T22" s="163" t="str">
         <f>+'9'!A5</f>
@@ -24202,7 +24202,7 @@
       <c r="B25" s="210"/>
       <c r="C25" s="211">
         <f>H25/40</f>
-        <v>11.25</v>
+        <v>9</v>
       </c>
       <c r="D25" s="205"/>
       <c r="E25" s="205"/>
@@ -24213,39 +24213,39 @@
       </c>
       <c r="H25" s="177">
         <f t="shared" si="3"/>
-        <v>450</v>
+        <v>360</v>
       </c>
       <c r="I25" s="178">
         <f t="shared" si="3"/>
-        <v>30436.009999999995</v>
+        <v>25343.300000000003</v>
       </c>
       <c r="J25" s="177">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K25" s="178">
         <f t="shared" si="3"/>
-        <v>49.429800000000014</v>
+        <v>0</v>
       </c>
       <c r="L25" s="179">
         <f t="shared" si="3"/>
-        <v>2392.5124000000001</v>
+        <v>2027.4639999999999</v>
       </c>
       <c r="M25" s="141">
         <f t="shared" si="3"/>
-        <v>27994.067799999997</v>
+        <v>23315.835999999999</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>6453.4520159999993</v>
+        <v>5408.2602200000001</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>237.96762976000002</v>
+        <v>143.62048110000001</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>34685.487445760002</v>
+        <v>28867.716701099998</v>
       </c>
       <c r="T25" s="163" t="str">
         <f>+'12'!A5</f>
@@ -24375,7 +24375,7 @@
       </c>
       <c r="U30" s="165">
         <f>SUM(U14:U28)</f>
-        <v>34685.487445760002</v>
+        <v>28867.716701099998</v>
       </c>
     </row>
     <row r="31" spans="1:21 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -24408,7 +24408,7 @@
       <c r="O32" s="222"/>
       <c r="P32" s="152">
         <f>I25</f>
-        <v>30436.009999999995</v>
+        <v>25343.300000000003</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24429,7 +24429,7 @@
       <c r="O33" s="224"/>
       <c r="P33" s="153">
         <f>L25</f>
-        <v>2392.5124000000001</v>
+        <v>2027.4639999999999</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24450,7 +24450,7 @@
       <c r="O34" s="224"/>
       <c r="P34" s="154">
         <f>K25</f>
-        <v>49.429800000000014</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24472,7 +24472,7 @@
       <c r="O35" s="224"/>
       <c r="P35" s="153">
         <f>P32-P33-P34</f>
-        <v>27994.067799999993</v>
+        <v>23315.836000000003</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24497,7 +24497,7 @@
       </c>
       <c r="P36" s="153">
         <f>N25</f>
-        <v>6453.4520159999993</v>
+        <v>5408.2602200000001</v>
       </c>
     </row>
     <row r="37" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24519,7 +24519,7 @@
       <c r="O37" s="226"/>
       <c r="P37" s="153">
         <f>P35+P36</f>
-        <v>34447.519815999993</v>
+        <v>28724.096220000003</v>
       </c>
     </row>
     <row r="38" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -24544,7 +24544,7 @@
       </c>
       <c r="P38" s="153">
         <f>O38*P37</f>
-        <v>861.18799539999986</v>
+        <v>718.10240550000015</v>
       </c>
     </row>
     <row r="39" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -24554,7 +24554,7 @@
       <c r="O39" s="204"/>
       <c r="P39" s="160">
         <f>P37+P38</f>
-        <v>35308.707811399996</v>
+        <v>29442.198625500005</v>
       </c>
     </row>
     <row r="40" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -24726,7 +24726,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -24754,7 +24754,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -25222,12 +25222,10 @@
         <v>72.64</v>
       </c>
       <c r="G19" s="114"/>
-      <c r="H19" s="115">
-        <v>8</v>
-      </c>
+      <c r="H19" s="115"/>
       <c r="I19" s="116">
         <f t="shared" si="3"/>
-        <v>581.12</v>
+        <v>0</v>
       </c>
       <c r="J19" s="117"/>
       <c r="K19" s="1">
@@ -25236,23 +25234,23 @@
       </c>
       <c r="L19" s="105">
         <f t="shared" si="5"/>
-        <v>46.489600000000003</v>
+        <v>0</v>
       </c>
       <c r="M19" s="118">
         <f t="shared" si="6"/>
-        <v>534.63040000000001</v>
+        <v>0</v>
       </c>
       <c r="N19" s="118">
         <f t="shared" si="0"/>
-        <v>117.61868800000001</v>
+        <v>0</v>
       </c>
       <c r="O19" s="119">
         <f t="shared" si="1"/>
-        <v>16.306227200000002</v>
+        <v>0</v>
       </c>
       <c r="P19" s="120">
         <f t="shared" si="2"/>
-        <v>668.5553152</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -25280,39 +25278,35 @@
         <v>72.64</v>
       </c>
       <c r="G20" s="114"/>
-      <c r="H20" s="115">
-        <v>8</v>
-      </c>
+      <c r="H20" s="115"/>
       <c r="I20" s="116">
         <f t="shared" si="3"/>
-        <v>581.12</v>
-      </c>
-      <c r="J20" s="117">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J20" s="117"/>
       <c r="K20" s="1">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L20" s="105">
         <f t="shared" si="5"/>
-        <v>46.489600000000003</v>
+        <v>0</v>
       </c>
       <c r="M20" s="118">
         <f t="shared" si="6"/>
-        <v>534.63040000000001</v>
+        <v>0</v>
       </c>
       <c r="N20" s="118">
         <f t="shared" si="0"/>
-        <v>133.59948800000001</v>
+        <v>0</v>
       </c>
       <c r="O20" s="119">
         <f t="shared" si="1"/>
-        <v>16.705747200000001</v>
+        <v>0</v>
       </c>
       <c r="P20" s="120">
         <f t="shared" si="2"/>
-        <v>684.93563520000009</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -25340,12 +25334,10 @@
         <v>72.64</v>
       </c>
       <c r="G21" s="114"/>
-      <c r="H21" s="115">
-        <v>8</v>
-      </c>
+      <c r="H21" s="115"/>
       <c r="I21" s="116">
         <f t="shared" si="3"/>
-        <v>581.12</v>
+        <v>0</v>
       </c>
       <c r="J21" s="117"/>
       <c r="K21" s="1">
@@ -25354,23 +25346,23 @@
       </c>
       <c r="L21" s="105">
         <f t="shared" si="5"/>
-        <v>46.489600000000003</v>
+        <v>0</v>
       </c>
       <c r="M21" s="118">
         <f t="shared" si="6"/>
-        <v>534.63040000000001</v>
+        <v>0</v>
       </c>
       <c r="N21" s="118">
         <f t="shared" si="0"/>
-        <v>117.61868800000001</v>
+        <v>0</v>
       </c>
       <c r="O21" s="119">
         <f t="shared" si="1"/>
-        <v>16.306227200000002</v>
+        <v>0</v>
       </c>
       <c r="P21" s="120">
         <f t="shared" si="2"/>
-        <v>668.5553152</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:19 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -25398,37 +25390,35 @@
         <v>39.230000000000004</v>
       </c>
       <c r="G22" s="114"/>
-      <c r="H22" s="115">
-        <v>12</v>
-      </c>
+      <c r="H22" s="115"/>
       <c r="I22" s="116">
         <f t="shared" si="3"/>
-        <v>470.76000000000005</v>
+        <v>0</v>
       </c>
       <c r="J22" s="117"/>
       <c r="K22" s="1">
         <f>I22*3.5%</f>
-        <v>16.476600000000005</v>
+        <v>0</v>
       </c>
       <c r="L22" s="120">
         <f>I22*5%</f>
-        <v>23.538000000000004</v>
+        <v>0</v>
       </c>
       <c r="M22" s="118">
         <f t="shared" si="6"/>
-        <v>430.74540000000002</v>
+        <v>0</v>
       </c>
       <c r="N22" s="118">
         <f t="shared" si="0"/>
-        <v>94.763987999999998</v>
+        <v>0</v>
       </c>
       <c r="O22" s="119">
         <f t="shared" si="1"/>
-        <v>13.137734700000003</v>
+        <v>0</v>
       </c>
       <c r="P22" s="120">
         <f t="shared" si="2"/>
-        <v>538.64712270000007</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:19 16384:16384" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -25558,36 +25548,36 @@
       </c>
       <c r="H25" s="136">
         <f t="shared" si="9"/>
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="I25" s="137">
         <f t="shared" si="9"/>
-        <v>2214.1200000000003</v>
+        <v>0</v>
       </c>
       <c r="J25" s="138"/>
       <c r="K25" s="139">
         <f t="shared" si="9"/>
-        <v>16.476600000000005</v>
+        <v>0</v>
       </c>
       <c r="L25" s="140">
         <f t="shared" si="9"/>
-        <v>163.00680000000003</v>
+        <v>0</v>
       </c>
       <c r="M25" s="141">
         <f t="shared" si="9"/>
-        <v>2034.6366</v>
+        <v>0</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>463.60085200000003</v>
+        <v>0</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>62.455936300000005</v>
+        <v>0</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>2560.6933883000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -25637,7 +25627,7 @@
       <c r="O28" s="222"/>
       <c r="P28" s="152">
         <f>I25</f>
-        <v>2214.1200000000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -25658,7 +25648,7 @@
       <c r="O29" s="224"/>
       <c r="P29" s="153">
         <f>L25</f>
-        <v>163.00680000000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -25679,7 +25669,7 @@
       <c r="O30" s="224"/>
       <c r="P30" s="154">
         <f>K25</f>
-        <v>16.476600000000005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -25701,7 +25691,7 @@
       <c r="O31" s="224"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
-        <v>2034.6366000000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -25726,7 +25716,7 @@
       </c>
       <c r="P32" s="153">
         <f>N25</f>
-        <v>463.60085200000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -25748,7 +25738,7 @@
       <c r="O33" s="226"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
-        <v>2498.2374520000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -25773,7 +25763,7 @@
       </c>
       <c r="P34" s="153">
         <f>O34*P33</f>
-        <v>62.455936300000012</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -25783,7 +25773,7 @@
       <c r="O35" s="204"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
-        <v>2560.6933883000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -25955,7 +25945,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -25983,7 +25973,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -27186,7 +27176,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -27214,7 +27204,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -27508,12 +27498,10 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G16" s="100"/>
-      <c r="H16" s="101">
-        <v>6</v>
-      </c>
+      <c r="H16" s="101"/>
       <c r="I16" s="102">
         <f>(G16*D16)*F16+H16*F16</f>
-        <v>314.77499999999998</v>
+        <v>0</v>
       </c>
       <c r="J16" s="103"/>
       <c r="K16" s="104">
@@ -27522,23 +27510,23 @@
       </c>
       <c r="L16" s="105">
         <f>I16*8%</f>
-        <v>25.181999999999999</v>
+        <v>0</v>
       </c>
       <c r="M16" s="106">
         <f>I16-K16-L16</f>
-        <v>289.59299999999996</v>
+        <v>0</v>
       </c>
       <c r="N16" s="106">
         <f t="shared" ref="N16:N24" si="0">(M16*$N$15)+(J16*F16)*$N$15</f>
-        <v>63.710459999999991</v>
+        <v>0</v>
       </c>
       <c r="O16" s="107">
         <f>(N16+M16)*$O$15</f>
-        <v>1.7665172999999998</v>
+        <v>0</v>
       </c>
       <c r="P16" s="105">
         <f t="shared" ref="P16:P24" si="1">M16+N16+O16</f>
-        <v>355.06997729999995</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="108"/>
       <c r="XFD16" t="s">
@@ -27570,12 +27558,10 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G17" s="114"/>
-      <c r="H17" s="115">
-        <v>6</v>
-      </c>
+      <c r="H17" s="115"/>
       <c r="I17" s="116">
         <f t="shared" ref="I17:I23" si="2">(G17*D17)*F17+H17*F17</f>
-        <v>314.77499999999998</v>
+        <v>0</v>
       </c>
       <c r="J17" s="117"/>
       <c r="K17" s="1">
@@ -27584,23 +27570,23 @@
       </c>
       <c r="L17" s="105">
         <f t="shared" ref="L17:L21" si="4">I17*8%</f>
-        <v>25.181999999999999</v>
+        <v>0</v>
       </c>
       <c r="M17" s="118">
         <f t="shared" ref="M17:M23" si="5">I17-K17-L17</f>
-        <v>289.59299999999996</v>
+        <v>0</v>
       </c>
       <c r="N17" s="118">
         <f t="shared" si="0"/>
-        <v>63.710459999999991</v>
+        <v>0</v>
       </c>
       <c r="O17" s="119">
         <f t="shared" ref="O17:O24" si="6">(N17+M17)*$O$15</f>
-        <v>1.7665172999999998</v>
+        <v>0</v>
       </c>
       <c r="P17" s="120">
         <f t="shared" si="1"/>
-        <v>355.06997729999995</v>
+        <v>0</v>
       </c>
       <c r="S17" s="64"/>
       <c r="XFD17" t="s">
@@ -27688,12 +27674,10 @@
         <v>72.64</v>
       </c>
       <c r="G19" s="114"/>
-      <c r="H19" s="115">
-        <v>6</v>
-      </c>
+      <c r="H19" s="115"/>
       <c r="I19" s="116">
         <f t="shared" si="2"/>
-        <v>435.84000000000003</v>
+        <v>0</v>
       </c>
       <c r="J19" s="117"/>
       <c r="K19" s="1">
@@ -27702,23 +27686,23 @@
       </c>
       <c r="L19" s="105">
         <f t="shared" si="4"/>
-        <v>34.867200000000004</v>
+        <v>0</v>
       </c>
       <c r="M19" s="118">
         <f t="shared" si="5"/>
-        <v>400.97280000000001</v>
+        <v>0</v>
       </c>
       <c r="N19" s="118">
         <f t="shared" si="0"/>
-        <v>88.214016000000001</v>
+        <v>0</v>
       </c>
       <c r="O19" s="119">
         <f t="shared" si="6"/>
-        <v>2.4459340800000002</v>
+        <v>0</v>
       </c>
       <c r="P19" s="120">
         <f t="shared" si="1"/>
-        <v>491.63275007999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -27746,12 +27730,10 @@
         <v>72.64</v>
       </c>
       <c r="G20" s="114"/>
-      <c r="H20" s="115">
-        <v>6</v>
-      </c>
+      <c r="H20" s="115"/>
       <c r="I20" s="116">
         <f t="shared" si="2"/>
-        <v>435.84000000000003</v>
+        <v>0</v>
       </c>
       <c r="J20" s="117"/>
       <c r="K20" s="1">
@@ -27760,23 +27742,23 @@
       </c>
       <c r="L20" s="105">
         <f t="shared" si="4"/>
-        <v>34.867200000000004</v>
+        <v>0</v>
       </c>
       <c r="M20" s="118">
         <f t="shared" si="5"/>
-        <v>400.97280000000001</v>
+        <v>0</v>
       </c>
       <c r="N20" s="118">
         <f t="shared" si="0"/>
-        <v>88.214016000000001</v>
+        <v>0</v>
       </c>
       <c r="O20" s="119">
         <f t="shared" si="6"/>
-        <v>2.4459340800000002</v>
+        <v>0</v>
       </c>
       <c r="P20" s="120">
         <f t="shared" si="1"/>
-        <v>491.63275007999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -27804,12 +27786,10 @@
         <v>72.64</v>
       </c>
       <c r="G21" s="114"/>
-      <c r="H21" s="115">
-        <v>6</v>
-      </c>
+      <c r="H21" s="115"/>
       <c r="I21" s="116">
         <f t="shared" si="2"/>
-        <v>435.84000000000003</v>
+        <v>0</v>
       </c>
       <c r="J21" s="117"/>
       <c r="K21" s="1">
@@ -27818,23 +27798,23 @@
       </c>
       <c r="L21" s="105">
         <f t="shared" si="4"/>
-        <v>34.867200000000004</v>
+        <v>0</v>
       </c>
       <c r="M21" s="118">
         <f t="shared" si="5"/>
-        <v>400.97280000000001</v>
+        <v>0</v>
       </c>
       <c r="N21" s="118">
         <f t="shared" si="0"/>
-        <v>88.214016000000001</v>
+        <v>0</v>
       </c>
       <c r="O21" s="119">
         <f t="shared" si="6"/>
-        <v>2.4459340800000002</v>
+        <v>0</v>
       </c>
       <c r="P21" s="120">
         <f t="shared" si="1"/>
-        <v>491.63275007999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -27862,37 +27842,35 @@
         <v>39.230000000000004</v>
       </c>
       <c r="G22" s="114"/>
-      <c r="H22" s="115">
-        <v>6</v>
-      </c>
+      <c r="H22" s="115"/>
       <c r="I22" s="116">
         <f t="shared" si="2"/>
-        <v>235.38000000000002</v>
+        <v>0</v>
       </c>
       <c r="J22" s="117"/>
       <c r="K22" s="1">
         <f>I22*3.5%</f>
-        <v>8.2383000000000024</v>
+        <v>0</v>
       </c>
       <c r="L22" s="120">
         <f>I22*5%</f>
-        <v>11.769000000000002</v>
+        <v>0</v>
       </c>
       <c r="M22" s="118">
         <f t="shared" si="5"/>
-        <v>215.37270000000001</v>
+        <v>0</v>
       </c>
       <c r="N22" s="118">
         <f t="shared" si="0"/>
-        <v>47.381993999999999</v>
+        <v>0</v>
       </c>
       <c r="O22" s="119">
         <f t="shared" si="6"/>
-        <v>1.3137734700000001</v>
+        <v>0</v>
       </c>
       <c r="P22" s="120">
         <f t="shared" si="1"/>
-        <v>264.06846747000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -28022,36 +28000,36 @@
       </c>
       <c r="H25" s="136">
         <f t="shared" si="9"/>
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="I25" s="137">
         <f t="shared" si="9"/>
-        <v>2172.4500000000003</v>
+        <v>0</v>
       </c>
       <c r="J25" s="138"/>
       <c r="K25" s="139">
         <f t="shared" si="9"/>
-        <v>8.2383000000000024</v>
+        <v>0</v>
       </c>
       <c r="L25" s="140">
         <f t="shared" si="9"/>
-        <v>166.7346</v>
+        <v>0</v>
       </c>
       <c r="M25" s="141">
         <f t="shared" si="9"/>
-        <v>1997.4771000000001</v>
+        <v>0</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>439.44496200000003</v>
+        <v>0</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>12.18461031</v>
+        <v>0</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>2449.1066723099998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -28101,7 +28079,7 @@
       <c r="O28" s="222"/>
       <c r="P28" s="152">
         <f>I25</f>
-        <v>2172.4500000000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -28122,7 +28100,7 @@
       <c r="O29" s="224"/>
       <c r="P29" s="153">
         <f>L25</f>
-        <v>166.7346</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -28143,7 +28121,7 @@
       <c r="O30" s="224"/>
       <c r="P30" s="154">
         <f>K25</f>
-        <v>8.2383000000000024</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -28165,7 +28143,7 @@
       <c r="O31" s="224"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
-        <v>1997.4771000000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -28190,7 +28168,7 @@
       </c>
       <c r="P32" s="153">
         <f>N25</f>
-        <v>439.44496200000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -28212,7 +28190,7 @@
       <c r="O33" s="226"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
-        <v>2436.9220620000006</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -28237,7 +28215,7 @@
       </c>
       <c r="P34" s="153">
         <f>O34*P33</f>
-        <v>12.184610310000004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -28247,7 +28225,7 @@
       <c r="O35" s="204"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
-        <v>2449.1066723100007</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -28418,7 +28396,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -28446,7 +28424,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -29084,37 +29062,35 @@
         <v>39.230000000000004</v>
       </c>
       <c r="G22" s="114"/>
-      <c r="H22" s="115">
-        <v>12</v>
-      </c>
+      <c r="H22" s="115"/>
       <c r="I22" s="116">
         <f t="shared" si="2"/>
-        <v>470.76000000000005</v>
+        <v>0</v>
       </c>
       <c r="J22" s="117"/>
       <c r="K22" s="1">
         <f>I22*3.5%</f>
-        <v>16.476600000000005</v>
+        <v>0</v>
       </c>
       <c r="L22" s="120">
         <f>I22*5%</f>
-        <v>23.538000000000004</v>
+        <v>0</v>
       </c>
       <c r="M22" s="118">
         <f t="shared" si="5"/>
-        <v>430.74540000000002</v>
+        <v>0</v>
       </c>
       <c r="N22" s="118">
         <f t="shared" si="0"/>
-        <v>94.763987999999998</v>
+        <v>0</v>
       </c>
       <c r="O22" s="119">
         <f t="shared" si="6"/>
-        <v>13.137734700000003</v>
+        <v>0</v>
       </c>
       <c r="P22" s="120">
         <f t="shared" si="1"/>
-        <v>538.64712270000007</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:19 16384:16384" hidden="1" x14ac:dyDescent="0.35">
@@ -29244,36 +29220,36 @@
       </c>
       <c r="H25" s="136">
         <f t="shared" si="9"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I25" s="137">
         <f t="shared" si="9"/>
-        <v>470.76000000000005</v>
+        <v>0</v>
       </c>
       <c r="J25" s="138"/>
       <c r="K25" s="139">
         <f t="shared" si="9"/>
-        <v>16.476600000000005</v>
+        <v>0</v>
       </c>
       <c r="L25" s="140">
         <f t="shared" si="9"/>
-        <v>23.538000000000004</v>
+        <v>0</v>
       </c>
       <c r="M25" s="141">
         <f t="shared" si="9"/>
-        <v>430.74540000000002</v>
+        <v>0</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>94.763987999999998</v>
+        <v>0</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>13.137734700000003</v>
+        <v>0</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>538.64712270000007</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -29323,7 +29299,7 @@
       <c r="O28" s="222"/>
       <c r="P28" s="152">
         <f>I25</f>
-        <v>470.76000000000005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -29344,7 +29320,7 @@
       <c r="O29" s="224"/>
       <c r="P29" s="153">
         <f>L25</f>
-        <v>23.538000000000004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -29365,7 +29341,7 @@
       <c r="O30" s="224"/>
       <c r="P30" s="154">
         <f>K25</f>
-        <v>16.476600000000005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -29387,7 +29363,7 @@
       <c r="O31" s="224"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
-        <v>430.74540000000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -29412,7 +29388,7 @@
       </c>
       <c r="P32" s="153">
         <f>N25</f>
-        <v>94.763987999999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -29434,7 +29410,7 @@
       <c r="O33" s="226"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
-        <v>525.50938800000006</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -29459,7 +29435,7 @@
       </c>
       <c r="P34" s="153">
         <f>O34*P33</f>
-        <v>13.137734700000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -29469,7 +29445,7 @@
       <c r="O35" s="204"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
-        <v>538.64712270000007</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -29642,7 +29618,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -29670,7 +29646,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -30867,7 +30843,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -30895,7 +30871,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -31533,37 +31509,35 @@
         <v>39.230000000000004</v>
       </c>
       <c r="G22" s="114"/>
-      <c r="H22" s="115">
-        <v>6</v>
-      </c>
+      <c r="H22" s="115"/>
       <c r="I22" s="116">
         <f t="shared" si="2"/>
-        <v>235.38000000000002</v>
+        <v>0</v>
       </c>
       <c r="J22" s="117"/>
       <c r="K22" s="1">
         <f>I22*3.5%</f>
-        <v>8.2383000000000024</v>
+        <v>0</v>
       </c>
       <c r="L22" s="120">
         <f>I22*5%</f>
-        <v>11.769000000000002</v>
+        <v>0</v>
       </c>
       <c r="M22" s="118">
         <f t="shared" si="5"/>
-        <v>215.37270000000001</v>
+        <v>0</v>
       </c>
       <c r="N22" s="118">
         <f t="shared" si="0"/>
-        <v>47.381993999999999</v>
+        <v>0</v>
       </c>
       <c r="O22" s="119">
         <f t="shared" si="6"/>
-        <v>6.5688673500000014</v>
+        <v>0</v>
       </c>
       <c r="P22" s="120">
         <f t="shared" si="1"/>
-        <v>269.32356135000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -31693,36 +31667,36 @@
       </c>
       <c r="H25" s="136">
         <f t="shared" si="9"/>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I25" s="137">
         <f t="shared" si="9"/>
-        <v>235.38000000000002</v>
+        <v>0</v>
       </c>
       <c r="J25" s="138"/>
       <c r="K25" s="139">
         <f t="shared" si="9"/>
-        <v>8.2383000000000024</v>
+        <v>0</v>
       </c>
       <c r="L25" s="140">
         <f t="shared" si="9"/>
-        <v>11.769000000000002</v>
+        <v>0</v>
       </c>
       <c r="M25" s="141">
         <f t="shared" si="9"/>
-        <v>215.37270000000001</v>
+        <v>0</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>47.381993999999999</v>
+        <v>0</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>6.5688673500000014</v>
+        <v>0</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>269.32356135000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -31772,7 +31746,7 @@
       <c r="O28" s="222"/>
       <c r="P28" s="152">
         <f>I25</f>
-        <v>235.38000000000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -31793,7 +31767,7 @@
       <c r="O29" s="224"/>
       <c r="P29" s="153">
         <f>L25</f>
-        <v>11.769000000000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -31814,7 +31788,7 @@
       <c r="O30" s="224"/>
       <c r="P30" s="154">
         <f>K25</f>
-        <v>8.2383000000000024</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -31836,7 +31810,7 @@
       <c r="O31" s="224"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
-        <v>215.37270000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -31861,7 +31835,7 @@
       </c>
       <c r="P32" s="153">
         <f>N25</f>
-        <v>47.381993999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -31883,7 +31857,7 @@
       <c r="O33" s="226"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
-        <v>262.75469400000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -31908,7 +31882,7 @@
       </c>
       <c r="P34" s="153">
         <f>O34*P33</f>
-        <v>6.5688673500000014</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -31918,7 +31892,7 @@
       <c r="O35" s="204"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
-        <v>269.32356135000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
